--- a/backend/data/financials_by_company/000819.SZ.xlsx
+++ b/backend/data/financials_by_company/000819.SZ.xlsx
@@ -692,658 +692,658 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>2249076.521254</v>
+        <v>274883.440269</v>
       </c>
       <c r="C2" t="n">
-        <v>0.36319</v>
+        <v>0.177605</v>
       </c>
       <c r="D2" t="n">
-        <v>177086112.67</v>
+        <v>114229296.03</v>
       </c>
       <c r="E2" t="n">
-        <v>6192569.7</v>
+        <v>1547723.58</v>
       </c>
       <c r="F2" t="n">
-        <v>6192569.7</v>
+        <v>1547723.58</v>
       </c>
       <c r="G2" t="n">
-        <v>63125607.38</v>
+        <v>63793543.11</v>
       </c>
       <c r="H2" t="n">
-        <v>94307941.86</v>
+        <v>27204844.36</v>
       </c>
       <c r="I2" t="n">
-        <v>3144757529.08</v>
+        <v>1730928101.08</v>
       </c>
       <c r="J2" t="n">
-        <v>183278682.37</v>
+        <v>115777019.61</v>
       </c>
       <c r="K2" t="n">
-        <v>88970740.51000001</v>
+        <v>88572175.25</v>
       </c>
       <c r="L2" t="n">
-        <v>-2121264.98</v>
+        <v>3546190.43</v>
       </c>
       <c r="M2" t="n">
-        <v>5380041</v>
+        <v>275086.76</v>
       </c>
       <c r="N2" t="n">
-        <v>3851861.97</v>
+        <v>4356191.04</v>
       </c>
       <c r="O2" t="n">
-        <v>59182114.201254</v>
+        <v>62520702.970269</v>
       </c>
       <c r="P2" t="n">
-        <v>63125607.38</v>
+        <v>63793543.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>3742718723.42</v>
+        <v>1871082360.56</v>
       </c>
       <c r="R2" t="n">
-        <v>985316.6899999999</v>
+        <v>2878812.45</v>
       </c>
       <c r="S2" t="n">
-        <v>84619216.43000001</v>
+        <v>88903478.04000001</v>
       </c>
       <c r="T2" t="n">
-        <v>371327102</v>
+        <v>299500202</v>
       </c>
       <c r="U2" t="n">
-        <v>371327102</v>
+        <v>299500202</v>
       </c>
       <c r="V2" t="n">
-        <v>0.17</v>
+        <v>0.213</v>
       </c>
       <c r="W2" t="n">
-        <v>0.17</v>
+        <v>0.213</v>
       </c>
       <c r="X2" t="n">
-        <v>63125607.38</v>
+        <v>63793543.11</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>63125607.38</v>
+        <v>63793543.11</v>
       </c>
       <c r="AA2" t="n">
-        <v>9894175.310000001</v>
+        <v>-8821541.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>53231432.07</v>
+        <v>72615084.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>53231432.07</v>
+        <v>72615084.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>30359267.44</v>
+        <v>15682004.05</v>
       </c>
       <c r="AE2" t="n">
-        <v>83590699.51000001</v>
+        <v>88297088.48999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1236454.75</v>
+        <v>-1128029.24</v>
       </c>
       <c r="AG2" t="n">
-        <v>6192569.7</v>
+        <v>-1215493.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>-5647404.57</v>
+        <v>161077.21</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1764454.56</v>
+        <v>135618.81</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1219289.43</v>
+        <v>918797.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>-2121264.98</v>
+        <v>3546190.43</v>
       </c>
       <c r="AL2" t="n">
-        <v>593085.95</v>
+        <v>534913.85</v>
       </c>
       <c r="AM2" t="n">
-        <v>5380041</v>
+        <v>275086.76</v>
       </c>
       <c r="AN2" t="n">
-        <v>3851861.97</v>
+        <v>4356191.04</v>
       </c>
       <c r="AO2" t="n">
-        <v>79917133.09999999</v>
+        <v>81288776.09999999</v>
       </c>
       <c r="AP2" t="n">
-        <v>597961194.34</v>
+        <v>140154259.48</v>
       </c>
       <c r="AQ2" t="n">
-        <v>378357192.88</v>
+        <v>15295199.88</v>
       </c>
       <c r="AR2" t="n">
-        <v>13208891.5</v>
+        <v>9261539.84</v>
       </c>
       <c r="AS2" t="n">
-        <v>13208891.5</v>
+        <v>9261539.84</v>
       </c>
       <c r="AT2" t="n">
-        <v>72538910.36</v>
+        <v>11865500.37</v>
       </c>
       <c r="AU2" t="n">
-        <v>65845924.41</v>
+        <v>32129850.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>10435693.09</v>
+        <v>6150052.75</v>
       </c>
       <c r="AW2" t="n">
-        <v>55410231.32</v>
+        <v>25979797.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>985316.6899999999</v>
+        <v>2878812.45</v>
       </c>
       <c r="AY2" t="n">
-        <v>677878327.4400001</v>
+        <v>221443035.58</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3144757529.08</v>
+        <v>1730928101.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>3822635856.52</v>
+        <v>1952371136.66</v>
       </c>
       <c r="BB2" t="n">
-        <v>3822635856.52</v>
+        <v>1952371136.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-804086.707754</v>
+        <v>-816090.728821</v>
       </c>
       <c r="C3" t="n">
-        <v>0.264133</v>
+        <v>0.11355</v>
       </c>
       <c r="D3" t="n">
-        <v>186235769.21</v>
+        <v>160936517.27</v>
       </c>
       <c r="E3" t="n">
-        <v>-3044244.32</v>
+        <v>-7187037.73</v>
       </c>
       <c r="F3" t="n">
-        <v>-3044244.32</v>
+        <v>-7187037.73</v>
       </c>
       <c r="G3" t="n">
-        <v>101076767.69</v>
+        <v>79983489.38</v>
       </c>
       <c r="H3" t="n">
-        <v>55735054.16</v>
+        <v>50316355.38</v>
       </c>
       <c r="I3" t="n">
-        <v>2515540805.32</v>
+        <v>2932049204.29</v>
       </c>
       <c r="J3" t="n">
-        <v>183191524.89</v>
+        <v>153749479.54</v>
       </c>
       <c r="K3" t="n">
-        <v>127456470.73</v>
+        <v>103433124.16</v>
       </c>
       <c r="L3" t="n">
-        <v>-2696902.44</v>
+        <v>3151816.86</v>
       </c>
       <c r="M3" t="n">
-        <v>4439085.41</v>
+        <v>481899.38</v>
       </c>
       <c r="N3" t="n">
-        <v>2368063.56</v>
+        <v>4248429.03</v>
       </c>
       <c r="O3" t="n">
-        <v>103316925.302246</v>
+        <v>86354436.381179</v>
       </c>
       <c r="P3" t="n">
-        <v>101076767.69</v>
+        <v>79983489.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>2938682942.63</v>
+        <v>3120461927.06</v>
       </c>
       <c r="R3" t="n">
-        <v>7603375.92</v>
+        <v>5165645.58</v>
       </c>
       <c r="S3" t="n">
-        <v>123076572.65</v>
+        <v>103404541.34</v>
       </c>
       <c r="T3" t="n">
-        <v>297284611</v>
+        <v>299563631</v>
       </c>
       <c r="U3" t="n">
-        <v>297284611</v>
+        <v>299563631</v>
       </c>
       <c r="V3" t="n">
-        <v>0.34</v>
+        <v>0.267</v>
       </c>
       <c r="W3" t="n">
-        <v>0.34</v>
+        <v>0.267</v>
       </c>
       <c r="X3" t="n">
-        <v>101076767.69</v>
+        <v>79983489.38</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>101076767.69</v>
+        <v>79983489.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>10552386.86</v>
+        <v>-11277586.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>90524380.83</v>
+        <v>91261076.04000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>90524380.83</v>
+        <v>91261076.04000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>32493004.49</v>
+        <v>11690148.74</v>
       </c>
       <c r="AE3" t="n">
-        <v>123017385.32</v>
+        <v>102951224.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>-292899.49</v>
+        <v>-656220.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>-3044244.32</v>
+        <v>-4794196.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>-55651.11</v>
+        <v>-13716.74</v>
       </c>
       <c r="AI3" t="n">
-        <v>664521.25</v>
+        <v>3472262.21</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2435374.18</v>
+        <v>1335650.76</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2696902.44</v>
+        <v>3151816.86</v>
       </c>
       <c r="AL3" t="n">
-        <v>625880.59</v>
+        <v>614712.79</v>
       </c>
       <c r="AM3" t="n">
-        <v>4439085.41</v>
+        <v>481899.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>2368063.56</v>
+        <v>4248429.03</v>
       </c>
       <c r="AO3" t="n">
-        <v>128718442.8</v>
+        <v>101458669.35</v>
       </c>
       <c r="AP3" t="n">
-        <v>423142137.31</v>
+        <v>188412722.77</v>
       </c>
       <c r="AQ3" t="n">
-        <v>212233017.61</v>
+        <v>19194112.25</v>
       </c>
       <c r="AR3" t="n">
-        <v>9371152</v>
+        <v>9124178.609999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>9371152</v>
+        <v>9124178.609999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>54819129.05</v>
+        <v>38795234.56</v>
       </c>
       <c r="AU3" t="n">
-        <v>65786503.81</v>
+        <v>43150408.34</v>
       </c>
       <c r="AV3" t="n">
-        <v>7221814.3</v>
+        <v>6124275.47</v>
       </c>
       <c r="AW3" t="n">
-        <v>58564689.51</v>
+        <v>37026132.87</v>
       </c>
       <c r="AX3" t="n">
-        <v>7603375.92</v>
+        <v>5165645.58</v>
       </c>
       <c r="AY3" t="n">
-        <v>551860580.11</v>
+        <v>289871392.12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2515540805.32</v>
+        <v>2932049204.29</v>
       </c>
       <c r="BA3" t="n">
-        <v>3067401385.43</v>
+        <v>3221920596.41</v>
       </c>
       <c r="BB3" t="n">
-        <v>3067401385.43</v>
+        <v>3221920596.41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-816090.728821</v>
+        <v>-804086.707754</v>
       </c>
       <c r="C4" t="n">
-        <v>0.11355</v>
+        <v>0.264133</v>
       </c>
       <c r="D4" t="n">
-        <v>160936517.27</v>
+        <v>186235769.21</v>
       </c>
       <c r="E4" t="n">
-        <v>-7187037.73</v>
+        <v>-3044244.32</v>
       </c>
       <c r="F4" t="n">
-        <v>-7187037.73</v>
+        <v>-3044244.32</v>
       </c>
       <c r="G4" t="n">
-        <v>79983489.38</v>
+        <v>101076767.69</v>
       </c>
       <c r="H4" t="n">
-        <v>50316355.38</v>
+        <v>55735054.16</v>
       </c>
       <c r="I4" t="n">
-        <v>2932049204.29</v>
+        <v>2515540805.32</v>
       </c>
       <c r="J4" t="n">
-        <v>153749479.54</v>
+        <v>183191524.89</v>
       </c>
       <c r="K4" t="n">
-        <v>103433124.16</v>
+        <v>127456470.73</v>
       </c>
       <c r="L4" t="n">
-        <v>3151816.86</v>
+        <v>-2696902.44</v>
       </c>
       <c r="M4" t="n">
-        <v>481899.38</v>
+        <v>4439085.41</v>
       </c>
       <c r="N4" t="n">
-        <v>4248429.03</v>
+        <v>2368063.56</v>
       </c>
       <c r="O4" t="n">
-        <v>86354436.381179</v>
+        <v>103316925.302246</v>
       </c>
       <c r="P4" t="n">
-        <v>79983489.38</v>
+        <v>101076767.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>3120461927.06</v>
+        <v>2938682942.63</v>
       </c>
       <c r="R4" t="n">
-        <v>5165645.58</v>
+        <v>7603375.92</v>
       </c>
       <c r="S4" t="n">
-        <v>103404541.34</v>
+        <v>123076572.65</v>
       </c>
       <c r="T4" t="n">
-        <v>299563631</v>
+        <v>297284611</v>
       </c>
       <c r="U4" t="n">
-        <v>299563631</v>
+        <v>297284611</v>
       </c>
       <c r="V4" t="n">
-        <v>0.267</v>
+        <v>0.34</v>
       </c>
       <c r="W4" t="n">
-        <v>0.267</v>
+        <v>0.34</v>
       </c>
       <c r="X4" t="n">
-        <v>79983489.38</v>
+        <v>101076767.69</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>79983489.38</v>
+        <v>101076767.69</v>
       </c>
       <c r="AA4" t="n">
-        <v>-11277586.66</v>
+        <v>10552386.86</v>
       </c>
       <c r="AB4" t="n">
-        <v>91261076.04000001</v>
+        <v>90524380.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>91261076.04000001</v>
+        <v>90524380.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>11690148.74</v>
+        <v>32493004.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>102951224.78</v>
+        <v>123017385.32</v>
       </c>
       <c r="AF4" t="n">
-        <v>-656220.62</v>
+        <v>-292899.49</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4794196.23</v>
+        <v>-3044244.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>-13716.74</v>
+        <v>-55651.11</v>
       </c>
       <c r="AI4" t="n">
-        <v>3472262.21</v>
+        <v>664521.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1335650.76</v>
+        <v>2435374.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>3151816.86</v>
+        <v>-2696902.44</v>
       </c>
       <c r="AL4" t="n">
-        <v>614712.79</v>
+        <v>625880.59</v>
       </c>
       <c r="AM4" t="n">
-        <v>481899.38</v>
+        <v>4439085.41</v>
       </c>
       <c r="AN4" t="n">
-        <v>4248429.03</v>
+        <v>2368063.56</v>
       </c>
       <c r="AO4" t="n">
-        <v>101458669.35</v>
+        <v>128718442.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>188412722.77</v>
+        <v>423142137.31</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19194112.25</v>
+        <v>212233017.61</v>
       </c>
       <c r="AR4" t="n">
-        <v>9124178.609999999</v>
+        <v>9371152</v>
       </c>
       <c r="AS4" t="n">
-        <v>9124178.609999999</v>
+        <v>9371152</v>
       </c>
       <c r="AT4" t="n">
-        <v>38795234.56</v>
+        <v>54819129.05</v>
       </c>
       <c r="AU4" t="n">
-        <v>43150408.34</v>
+        <v>65786503.81</v>
       </c>
       <c r="AV4" t="n">
-        <v>6124275.47</v>
+        <v>7221814.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>37026132.87</v>
+        <v>58564689.51</v>
       </c>
       <c r="AX4" t="n">
-        <v>5165645.58</v>
+        <v>7603375.92</v>
       </c>
       <c r="AY4" t="n">
-        <v>289871392.12</v>
+        <v>551860580.11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2932049204.29</v>
+        <v>2515540805.32</v>
       </c>
       <c r="BA4" t="n">
-        <v>3221920596.41</v>
+        <v>3067401385.43</v>
       </c>
       <c r="BB4" t="n">
-        <v>3221920596.41</v>
+        <v>3067401385.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>274883.440269</v>
+        <v>2249076.521254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.177605</v>
+        <v>0.36319</v>
       </c>
       <c r="D5" t="n">
-        <v>114229296.03</v>
+        <v>177086112.67</v>
       </c>
       <c r="E5" t="n">
-        <v>1547723.58</v>
+        <v>6192569.7</v>
       </c>
       <c r="F5" t="n">
-        <v>1547723.58</v>
+        <v>6192569.7</v>
       </c>
       <c r="G5" t="n">
-        <v>63793543.11</v>
+        <v>63125607.38</v>
       </c>
       <c r="H5" t="n">
-        <v>27204844.36</v>
+        <v>94307941.86</v>
       </c>
       <c r="I5" t="n">
-        <v>1730928101.08</v>
+        <v>3144757529.08</v>
       </c>
       <c r="J5" t="n">
-        <v>115777019.61</v>
+        <v>183278682.37</v>
       </c>
       <c r="K5" t="n">
-        <v>88572175.25</v>
+        <v>88970740.51000001</v>
       </c>
       <c r="L5" t="n">
-        <v>3546190.43</v>
+        <v>-2121264.98</v>
       </c>
       <c r="M5" t="n">
-        <v>275086.76</v>
+        <v>5380041</v>
       </c>
       <c r="N5" t="n">
-        <v>4356191.04</v>
+        <v>3851861.97</v>
       </c>
       <c r="O5" t="n">
-        <v>62520702.970269</v>
+        <v>59182114.201254</v>
       </c>
       <c r="P5" t="n">
-        <v>63793543.11</v>
+        <v>63125607.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1871082360.56</v>
+        <v>3742718723.42</v>
       </c>
       <c r="R5" t="n">
-        <v>2878812.45</v>
+        <v>985316.6899999999</v>
       </c>
       <c r="S5" t="n">
-        <v>88903478.04000001</v>
+        <v>84619216.43000001</v>
       </c>
       <c r="T5" t="n">
-        <v>299500202</v>
+        <v>371327102</v>
       </c>
       <c r="U5" t="n">
-        <v>299500202</v>
+        <v>371327102</v>
       </c>
       <c r="V5" t="n">
-        <v>0.213</v>
+        <v>0.17</v>
       </c>
       <c r="W5" t="n">
-        <v>0.213</v>
+        <v>0.17</v>
       </c>
       <c r="X5" t="n">
-        <v>63793543.11</v>
+        <v>63125607.38</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>63793543.11</v>
+        <v>63125607.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>-8821541.33</v>
+        <v>9894175.310000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>72615084.44</v>
+        <v>53231432.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>72615084.44</v>
+        <v>53231432.07</v>
       </c>
       <c r="AD5" t="n">
-        <v>15682004.05</v>
+        <v>30359267.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>88297088.48999999</v>
+        <v>83590699.51000001</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1128029.24</v>
+        <v>-1236454.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1215493.27</v>
+        <v>6192569.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>161077.21</v>
+        <v>-5647404.57</v>
       </c>
       <c r="AI5" t="n">
-        <v>135618.81</v>
+        <v>-1764454.56</v>
       </c>
       <c r="AJ5" t="n">
-        <v>918797.25</v>
+        <v>1219289.43</v>
       </c>
       <c r="AK5" t="n">
-        <v>3546190.43</v>
+        <v>-2121264.98</v>
       </c>
       <c r="AL5" t="n">
-        <v>534913.85</v>
+        <v>593085.95</v>
       </c>
       <c r="AM5" t="n">
-        <v>275086.76</v>
+        <v>5380041</v>
       </c>
       <c r="AN5" t="n">
-        <v>4356191.04</v>
+        <v>3851861.97</v>
       </c>
       <c r="AO5" t="n">
-        <v>81288776.09999999</v>
+        <v>79917133.09999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>140154259.48</v>
+        <v>597961194.34</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15295199.88</v>
+        <v>378357192.88</v>
       </c>
       <c r="AR5" t="n">
-        <v>9261539.84</v>
+        <v>13208891.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>9261539.84</v>
+        <v>13208891.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>11865500.37</v>
+        <v>72538910.36</v>
       </c>
       <c r="AU5" t="n">
-        <v>32129850.5</v>
+        <v>65845924.41</v>
       </c>
       <c r="AV5" t="n">
-        <v>6150052.75</v>
+        <v>10435693.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>25979797.75</v>
+        <v>55410231.32</v>
       </c>
       <c r="AX5" t="n">
-        <v>2878812.45</v>
+        <v>985316.6899999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>221443035.58</v>
+        <v>677878327.4400001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1730928101.08</v>
+        <v>3144757529.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>1952371136.66</v>
+        <v>3822635856.52</v>
       </c>
       <c r="BB5" t="n">
-        <v>1952371136.66</v>
+        <v>3822635856.52</v>
       </c>
     </row>
   </sheetData>
@@ -1729,314 +1729,404 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>299150255</v>
+      </c>
+      <c r="C2" t="n">
+        <v>299150255</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14219679.27</v>
+      </c>
+      <c r="E2" t="n">
+        <v>817179144.25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>907477797.48</v>
+      </c>
+      <c r="G2" t="n">
+        <v>300739020.79</v>
+      </c>
+      <c r="H2" t="n">
+        <v>817179144.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3245706.62</v>
+      </c>
+      <c r="J2" t="n">
+        <v>897477797.48</v>
+      </c>
+      <c r="K2" t="n">
+        <v>897477797.48</v>
+      </c>
+      <c r="L2" t="n">
+        <v>945913629.41</v>
+      </c>
+      <c r="M2" t="n">
+        <v>48435831.93</v>
+      </c>
+      <c r="N2" t="n">
+        <v>897477797.48</v>
+      </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>1028097678.01</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>340308672.47</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>299150255</v>
+      </c>
+      <c r="S2" t="n">
+        <v>299150255</v>
+      </c>
+      <c r="T2" t="n">
+        <v>237639812.25</v>
+      </c>
+      <c r="U2" t="n">
+        <v>13532482.19</v>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>10286775.57</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3245706.62</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3245706.62</v>
+      </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>224107330.06</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2973806.34</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>10973972.65</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>176128048.34</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>39999559.45</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>21178501.78</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>114949987.11</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1183553441.66</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>658707090.8099999</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>78845906.09999999</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>9285771.42</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>280441.28</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>51861760.74</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>51861760.74</v>
+      </c>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>80298653.23</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>80073653.23</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>225000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>438134558.04</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-336383897.56</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>774518455.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>16560048.74</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>37966497.06</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>444875631.86</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>275116277.94</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>275116277.94</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>524846350.85</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3025149.55</v>
+      </c>
       <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>9552411.82</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>148655044.03</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>4373273.01</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>74491647.93000001</v>
-      </c>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="n">
-        <v>-8000429.12</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>154632882.71</v>
-      </c>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="n">
-        <v>996866.12</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>250584454.98</v>
-      </c>
+      <c r="BG2" t="n">
+        <v>34908316.12</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>69849482.34</v>
+      </c>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="n">
+        <v>8697449.449999999</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>19722014.47</v>
+      </c>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="n">
+        <v>388643938.92</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>113392841.5</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>275251097.42</v>
+      </c>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>369697506</v>
+        <v>306325255</v>
       </c>
       <c r="C3" t="n">
-        <v>369697506</v>
+        <v>306325255</v>
       </c>
       <c r="D3" t="n">
-        <v>268897179.54</v>
+        <v>59463989.64</v>
       </c>
       <c r="E3" t="n">
-        <v>1849730345.96</v>
+        <v>787474769.48</v>
       </c>
       <c r="F3" t="n">
-        <v>2391952548.85</v>
+        <v>1045288458.99</v>
       </c>
       <c r="G3" t="n">
-        <v>88590910.88</v>
+        <v>173367284.62</v>
       </c>
       <c r="H3" t="n">
-        <v>1849730345.96</v>
+        <v>787474769.48</v>
       </c>
       <c r="I3" t="n">
-        <v>3041430.32</v>
+        <v>2026217.69</v>
       </c>
       <c r="J3" t="n">
-        <v>2149780588.96</v>
+        <v>989788458.99</v>
       </c>
       <c r="K3" t="n">
-        <v>2272168744.4</v>
+        <v>1038788458.99</v>
       </c>
       <c r="L3" t="n">
-        <v>2271959708.98</v>
+        <v>1079256513.68</v>
       </c>
       <c r="M3" t="n">
-        <v>122179120.02</v>
+        <v>89468054.69</v>
       </c>
       <c r="N3" t="n">
-        <v>2149780588.96</v>
+        <v>989788458.99</v>
       </c>
       <c r="O3" t="n">
-        <v>50281775</v>
+        <v>46996250</v>
       </c>
       <c r="P3" t="n">
-        <v>514052478.04</v>
+        <v>412097541.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1007173523.01</v>
+        <v>73108780.37</v>
       </c>
       <c r="R3" t="n">
-        <v>369697506</v>
+        <v>306325255</v>
       </c>
       <c r="S3" t="n">
-        <v>369697506</v>
+        <v>306325255</v>
       </c>
       <c r="T3" t="n">
-        <v>799354245.41</v>
+        <v>308126467.02</v>
       </c>
       <c r="U3" t="n">
-        <v>141170291.12</v>
+        <v>62371501.98</v>
       </c>
       <c r="V3" t="n">
-        <v>367450</v>
-      </c>
-      <c r="W3" t="n">
-        <v>10120869.57</v>
-      </c>
+        <v>373250</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>5252385.79</v>
+        <v>10972034.29</v>
       </c>
       <c r="Y3" t="n">
-        <v>125429585.76</v>
+        <v>51026217.69</v>
       </c>
       <c r="Z3" t="n">
-        <v>3041430.32</v>
+        <v>2026217.69</v>
       </c>
       <c r="AA3" t="n">
-        <v>122388155.44</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>49000000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>49000000</v>
+      </c>
       <c r="AC3" t="n">
-        <v>658183954.29</v>
+        <v>245754965.04</v>
       </c>
       <c r="AD3" t="n">
-        <v>14687548.91</v>
+        <v>5172273.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>143467593.78</v>
+        <v>8437771.949999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>119783804.45</v>
+        <v>6500000</v>
       </c>
       <c r="AG3" t="n">
-        <v>442861937.05</v>
+        <v>194278383.41</v>
       </c>
       <c r="AH3" t="n">
-        <v>106362050.93</v>
+        <v>92589544.79000001</v>
       </c>
       <c r="AI3" t="n">
-        <v>37588873.36</v>
+        <v>20515204.23</v>
       </c>
       <c r="AJ3" t="n">
-        <v>298911012.76</v>
+        <v>81173634.39</v>
       </c>
       <c r="AK3" t="n">
-        <v>3071313954.39</v>
+        <v>1387382980.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>2324539089.22</v>
+        <v>968260731.04</v>
       </c>
       <c r="AM3" t="n">
-        <v>12874349.35</v>
+        <v>108150537.45</v>
       </c>
       <c r="AN3" t="n">
-        <v>7918359.26</v>
+        <v>8370652.31</v>
       </c>
       <c r="AO3" t="n">
-        <v>15360530.69</v>
+        <v>10140676.54</v>
       </c>
       <c r="AP3" t="n">
-        <v>55905325</v>
+        <v>54543807.39</v>
       </c>
       <c r="AQ3" t="n">
-        <v>55905325</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>63248530.22</v>
-      </c>
+        <v>54543807.39</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>300050243</v>
+        <v>202313689.51</v>
       </c>
       <c r="AT3" t="n">
-        <v>299825243</v>
+        <v>202088689.51</v>
       </c>
       <c r="AU3" t="n">
         <v>225000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1869181751.7</v>
+        <v>584741367.84</v>
       </c>
       <c r="AW3" t="n">
-        <v>-490351408.32</v>
+        <v>-365409199.11</v>
       </c>
       <c r="AX3" t="n">
-        <v>2359533160.02</v>
+        <v>950150566.95</v>
       </c>
       <c r="AY3" t="n">
-        <v>936629495.0700001</v>
+        <v>149355212.29</v>
       </c>
       <c r="AZ3" t="n">
-        <v>57283089.76</v>
+        <v>41236368.89</v>
       </c>
       <c r="BA3" t="n">
-        <v>727249177.01</v>
+        <v>479179114.88</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>638371398.1799999</v>
+        <v>280379870.89</v>
       </c>
       <c r="BD3" t="n">
-        <v>746774865.17</v>
+        <v>419122249.66</v>
       </c>
       <c r="BE3" t="n">
-        <v>123147863.82</v>
+        <v>11829901.11</v>
       </c>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
-        <v>31356995.61</v>
+        <v>11380672.16</v>
       </c>
       <c r="BH3" t="n">
-        <v>175022395.76</v>
+        <v>66130117.11</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8612602.220000001</v>
+        <v>502215.42</v>
       </c>
       <c r="BK3" t="n">
-        <v>111462932.7</v>
+        <v>49962912.73</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="n">
-        <v>54946860.84</v>
+        <v>15664988.96</v>
       </c>
       <c r="BN3" t="n">
-        <v>52291434.51</v>
+        <v>7816082.49</v>
       </c>
       <c r="BO3" t="n">
-        <v>90572174.41</v>
+        <v>82734582.20999999</v>
       </c>
       <c r="BP3" t="n">
-        <v>-5024263.34</v>
+        <v>-4789519.87</v>
       </c>
       <c r="BQ3" t="n">
-        <v>95596437.75</v>
+        <v>87524102.08</v>
       </c>
       <c r="BR3" t="n">
-        <v>274384001.06</v>
+        <v>239230894.58</v>
       </c>
       <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="n">
-        <v>274384001.06</v>
+        <v>239230894.58</v>
       </c>
       <c r="BU3" t="n">
-        <v>618.52</v>
+        <v>25539119.73</v>
       </c>
       <c r="BV3" t="n">
-        <v>274383382.54</v>
+        <v>213691774.85</v>
       </c>
     </row>
     <row r="4">
@@ -2255,405 +2345,315 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>306325255</v>
+        <v>369697506</v>
       </c>
       <c r="C5" t="n">
-        <v>306325255</v>
+        <v>369697506</v>
       </c>
       <c r="D5" t="n">
-        <v>59463989.64</v>
+        <v>268897179.54</v>
       </c>
       <c r="E5" t="n">
-        <v>787474769.48</v>
+        <v>1849730345.96</v>
       </c>
       <c r="F5" t="n">
-        <v>1045288458.99</v>
+        <v>2391952548.85</v>
       </c>
       <c r="G5" t="n">
-        <v>173367284.62</v>
+        <v>88590910.88</v>
       </c>
       <c r="H5" t="n">
-        <v>787474769.48</v>
+        <v>1849730345.96</v>
       </c>
       <c r="I5" t="n">
-        <v>2026217.69</v>
+        <v>3041430.32</v>
       </c>
       <c r="J5" t="n">
-        <v>989788458.99</v>
+        <v>2149780588.96</v>
       </c>
       <c r="K5" t="n">
-        <v>1038788458.99</v>
+        <v>2272168744.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1079256513.68</v>
+        <v>2271959708.98</v>
       </c>
       <c r="M5" t="n">
-        <v>89468054.69</v>
+        <v>122179120.02</v>
       </c>
       <c r="N5" t="n">
-        <v>989788458.99</v>
+        <v>2149780588.96</v>
       </c>
       <c r="O5" t="n">
-        <v>46996250</v>
+        <v>50281775</v>
       </c>
       <c r="P5" t="n">
-        <v>412097541.5</v>
+        <v>514052478.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>73108780.37</v>
+        <v>1007173523.01</v>
       </c>
       <c r="R5" t="n">
-        <v>306325255</v>
+        <v>369697506</v>
       </c>
       <c r="S5" t="n">
-        <v>306325255</v>
+        <v>369697506</v>
       </c>
       <c r="T5" t="n">
-        <v>308126467.02</v>
+        <v>799354245.41</v>
       </c>
       <c r="U5" t="n">
-        <v>62371501.98</v>
+        <v>141170291.12</v>
       </c>
       <c r="V5" t="n">
-        <v>373250</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>367450</v>
+      </c>
+      <c r="W5" t="n">
+        <v>10120869.57</v>
+      </c>
       <c r="X5" t="n">
-        <v>10972034.29</v>
+        <v>5252385.79</v>
       </c>
       <c r="Y5" t="n">
-        <v>51026217.69</v>
+        <v>125429585.76</v>
       </c>
       <c r="Z5" t="n">
-        <v>2026217.69</v>
+        <v>3041430.32</v>
       </c>
       <c r="AA5" t="n">
-        <v>49000000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>49000000</v>
-      </c>
+        <v>122388155.44</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>245754965.04</v>
+        <v>658183954.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>5172273.28</v>
+        <v>14687548.91</v>
       </c>
       <c r="AE5" t="n">
-        <v>8437771.949999999</v>
+        <v>143467593.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>6500000</v>
+        <v>119783804.45</v>
       </c>
       <c r="AG5" t="n">
-        <v>194278383.41</v>
+        <v>442861937.05</v>
       </c>
       <c r="AH5" t="n">
-        <v>92589544.79000001</v>
+        <v>106362050.93</v>
       </c>
       <c r="AI5" t="n">
-        <v>20515204.23</v>
+        <v>37588873.36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>81173634.39</v>
+        <v>298911012.76</v>
       </c>
       <c r="AK5" t="n">
-        <v>1387382980.7</v>
+        <v>3071313954.39</v>
       </c>
       <c r="AL5" t="n">
-        <v>968260731.04</v>
+        <v>2324539089.22</v>
       </c>
       <c r="AM5" t="n">
-        <v>108150537.45</v>
+        <v>12874349.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>8370652.31</v>
+        <v>7918359.26</v>
       </c>
       <c r="AO5" t="n">
-        <v>10140676.54</v>
+        <v>15360530.69</v>
       </c>
       <c r="AP5" t="n">
-        <v>54543807.39</v>
+        <v>55905325</v>
       </c>
       <c r="AQ5" t="n">
-        <v>54543807.39</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>55905325</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>63248530.22</v>
+      </c>
       <c r="AS5" t="n">
-        <v>202313689.51</v>
+        <v>300050243</v>
       </c>
       <c r="AT5" t="n">
-        <v>202088689.51</v>
+        <v>299825243</v>
       </c>
       <c r="AU5" t="n">
         <v>225000</v>
       </c>
       <c r="AV5" t="n">
-        <v>584741367.84</v>
+        <v>1869181751.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>-365409199.11</v>
+        <v>-490351408.32</v>
       </c>
       <c r="AX5" t="n">
-        <v>950150566.95</v>
+        <v>2359533160.02</v>
       </c>
       <c r="AY5" t="n">
-        <v>149355212.29</v>
+        <v>936629495.0700001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>41236368.89</v>
+        <v>57283089.76</v>
       </c>
       <c r="BA5" t="n">
-        <v>479179114.88</v>
+        <v>727249177.01</v>
       </c>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>280379870.89</v>
+        <v>638371398.1799999</v>
       </c>
       <c r="BD5" t="n">
-        <v>419122249.66</v>
+        <v>746774865.17</v>
       </c>
       <c r="BE5" t="n">
-        <v>11829901.11</v>
+        <v>123147863.82</v>
       </c>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>11380672.16</v>
+        <v>31356995.61</v>
       </c>
       <c r="BH5" t="n">
-        <v>66130117.11</v>
+        <v>175022395.76</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>502215.42</v>
+        <v>8612602.220000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>49962912.73</v>
+        <v>111462932.7</v>
       </c>
       <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="n">
-        <v>15664988.96</v>
+        <v>54946860.84</v>
       </c>
       <c r="BN5" t="n">
-        <v>7816082.49</v>
+        <v>52291434.51</v>
       </c>
       <c r="BO5" t="n">
-        <v>82734582.20999999</v>
+        <v>90572174.41</v>
       </c>
       <c r="BP5" t="n">
-        <v>-4789519.87</v>
+        <v>-5024263.34</v>
       </c>
       <c r="BQ5" t="n">
-        <v>87524102.08</v>
+        <v>95596437.75</v>
       </c>
       <c r="BR5" t="n">
-        <v>239230894.58</v>
+        <v>274384001.06</v>
       </c>
       <c r="BS5" t="inlineStr"/>
       <c r="BT5" t="n">
-        <v>239230894.58</v>
+        <v>274384001.06</v>
       </c>
       <c r="BU5" t="n">
-        <v>25539119.73</v>
+        <v>618.52</v>
       </c>
       <c r="BV5" t="n">
-        <v>213691774.85</v>
+        <v>274383382.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>299150255</v>
-      </c>
-      <c r="C6" t="n">
-        <v>299150255</v>
-      </c>
-      <c r="D6" t="n">
-        <v>14219679.27</v>
-      </c>
-      <c r="E6" t="n">
-        <v>817179144.25</v>
-      </c>
-      <c r="F6" t="n">
-        <v>907477797.48</v>
-      </c>
-      <c r="G6" t="n">
-        <v>300739020.79</v>
-      </c>
-      <c r="H6" t="n">
-        <v>817179144.25</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3245706.62</v>
-      </c>
-      <c r="J6" t="n">
-        <v>897477797.48</v>
-      </c>
-      <c r="K6" t="n">
-        <v>897477797.48</v>
-      </c>
-      <c r="L6" t="n">
-        <v>945913629.41</v>
-      </c>
-      <c r="M6" t="n">
-        <v>48435831.93</v>
-      </c>
-      <c r="N6" t="n">
-        <v>897477797.48</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>340308672.47</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
-        <v>299150255</v>
-      </c>
-      <c r="S6" t="n">
-        <v>299150255</v>
-      </c>
-      <c r="T6" t="n">
-        <v>237639812.25</v>
-      </c>
-      <c r="U6" t="n">
-        <v>13532482.19</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>1028097678.01</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="n">
-        <v>10286775.57</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3245706.62</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3245706.62</v>
-      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>224107330.06</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2973806.34</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>10973972.65</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>176128048.34</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>39999559.45</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>21178501.78</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>114949987.11</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1183553441.66</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>658707090.8099999</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>78845906.09999999</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>9285771.42</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>280441.28</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>51861760.74</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>51861760.74</v>
-      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="n">
-        <v>80298653.23</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>80073653.23</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>225000</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>438134558.04</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-336383897.56</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>774518455.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>16560048.74</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>37966497.06</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>444875631.86</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>275116277.94</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>275116277.94</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>524846350.85</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>3025149.55</v>
-      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="n">
-        <v>34908316.12</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>69849482.34</v>
-      </c>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="n">
-        <v>8697449.449999999</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>19722014.47</v>
-      </c>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="n">
-        <v>388643938.92</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>113392841.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>275251097.42</v>
-      </c>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>9552411.82</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>148655044.03</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>4373273.01</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>74491647.93000001</v>
+      </c>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="n">
+        <v>-8000429.12</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>154632882.71</v>
+      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="n">
+        <v>996866.12</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>250584454.98</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2908,570 +2908,570 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-425429785.06</v>
+        <v>-303205510.11</v>
       </c>
       <c r="C2" t="n">
-        <v>-536974520.15</v>
+        <v>-5000000</v>
       </c>
       <c r="D2" t="n">
-        <v>189769970.75</v>
+        <v>10000000</v>
       </c>
       <c r="E2" t="n">
-        <v>-459897026.58</v>
+        <v>-357111195.6</v>
       </c>
       <c r="F2" t="n">
-        <v>274382882.54</v>
+        <v>242141097.42</v>
       </c>
       <c r="G2" t="n">
-        <v>1101503463.97</v>
+        <v>272425613.46</v>
       </c>
       <c r="H2" t="n">
-        <v>32577.7</v>
+        <v>34427.88</v>
       </c>
       <c r="I2" t="n">
-        <v>-827153159.13</v>
+        <v>-30318943.92</v>
       </c>
       <c r="J2" t="n">
-        <v>-359285823.77</v>
+        <v>-1738743.64</v>
       </c>
       <c r="K2" t="n">
-        <v>33479602.6</v>
+        <v>-3373234.14</v>
       </c>
       <c r="L2" t="n">
-        <v>-45560876.97</v>
+        <v>-3365509.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-347204549.4</v>
+        <v>5000000</v>
       </c>
       <c r="N2" t="n">
-        <v>-347204549.4</v>
+        <v>5000000</v>
       </c>
       <c r="O2" t="n">
-        <v>-536974520.15</v>
+        <v>-5000000</v>
       </c>
       <c r="P2" t="n">
-        <v>189769970.75</v>
+        <v>10000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-502334576.88</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>-82485885.77</v>
+      </c>
+      <c r="R2" t="n">
+        <v>304753166.48</v>
+      </c>
       <c r="S2" t="n">
-        <v>-57775000</v>
+        <v>-31074193.65</v>
       </c>
       <c r="T2" t="n">
-        <v>1225000</v>
+        <v>203659743.35</v>
       </c>
       <c r="U2" t="n">
-        <v>-59000000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>-234733937</v>
+      </c>
+      <c r="V2" t="n">
+        <v>313565.34</v>
+      </c>
+      <c r="W2" t="n">
+        <v>313565.34</v>
+      </c>
       <c r="X2" t="n">
-        <v>-444559576.88</v>
+        <v>-356478423.94</v>
       </c>
       <c r="Y2" t="n">
-        <v>15337449.7</v>
+        <v>632771.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>-459897026.58</v>
+        <v>-357111195.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>34467241.52</v>
+        <v>53905685.49</v>
       </c>
       <c r="AB2" t="n">
-        <v>-139481751.94</v>
+        <v>-42264367.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>-4444175.69</v>
+        <v>1680062.96</v>
       </c>
       <c r="AD2" t="n">
-        <v>30385536.5</v>
+        <v>38767069.54</v>
       </c>
       <c r="AE2" t="n">
-        <v>-135406384.79</v>
+        <v>-24235407.55</v>
       </c>
       <c r="AF2" t="n">
-        <v>-30016727.96</v>
+        <v>-58476092.49</v>
       </c>
       <c r="AG2" t="n">
-        <v>6678438.54</v>
+        <v>4939765.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>94307941.86</v>
+        <v>27204844.36</v>
       </c>
       <c r="AI2" t="n">
-        <v>6977650.9</v>
+        <v>2752801.41</v>
       </c>
       <c r="AJ2" t="n">
-        <v>87330290.95999999</v>
+        <v>24452042.95</v>
       </c>
       <c r="AK2" t="n">
-        <v>-705882.63</v>
+        <v>-5978680.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>-4207286.14</v>
+        <v>1699472.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>53231432.07</v>
+        <v>72615084.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>34467241.52</v>
+        <v>53905685.49</v>
       </c>
       <c r="AO2" t="n">
-        <v>-545622122.97</v>
+        <v>-31595499.2</v>
       </c>
       <c r="AP2" t="n">
-        <v>-3690697504.2</v>
+        <v>-2072263424.89</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-147985815.35</v>
+        <v>-87206563.54000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>-158850561.12</v>
+        <v>-107555788.14</v>
       </c>
       <c r="AS2" t="n">
-        <v>-3383861127.73</v>
+        <v>-1877501073.21</v>
       </c>
       <c r="AT2" t="n">
-        <v>4270786868.69</v>
+        <v>2157764609.58</v>
       </c>
       <c r="AU2" t="n">
-        <v>107523271.59</v>
+        <v>22955655.71</v>
       </c>
       <c r="AV2" t="n">
-        <v>4163263597.1</v>
+        <v>2134808953.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-651841823.5</v>
+        <v>-273861879.64</v>
       </c>
       <c r="C3" t="n">
-        <v>-80500000</v>
+        <v>-10500000</v>
       </c>
       <c r="D3" t="n">
-        <v>610264822.12</v>
+        <v>57000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-818612963.1799999</v>
+        <v>-382674269.67</v>
       </c>
       <c r="F3" t="n">
-        <v>1101503463.97</v>
+        <v>216120894.58</v>
       </c>
       <c r="G3" t="n">
-        <v>216120894.58</v>
+        <v>242141097.42</v>
       </c>
       <c r="H3" t="n">
-        <v>-142179.04</v>
+        <v>1016668.09</v>
       </c>
       <c r="I3" t="n">
-        <v>885524748.4299999</v>
+        <v>-27036870.93</v>
       </c>
       <c r="J3" t="n">
-        <v>1540474701.68</v>
+        <v>119376388.57</v>
       </c>
       <c r="K3" t="n">
-        <v>1016104011.11</v>
+        <v>73300931.59999999</v>
       </c>
       <c r="L3" t="n">
-        <v>-5394131.55</v>
+        <v>-424543.03</v>
       </c>
       <c r="M3" t="n">
-        <v>529764822.12</v>
+        <v>46500000</v>
       </c>
       <c r="N3" t="n">
-        <v>529764822.12</v>
+        <v>46500000</v>
       </c>
       <c r="O3" t="n">
-        <v>-80500000</v>
+        <v>-10500000</v>
       </c>
       <c r="P3" t="n">
-        <v>610264822.12</v>
+        <v>57000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-821721092.9299999</v>
+        <v>-255225649.53</v>
       </c>
       <c r="R3" t="n">
-        <v>602436.25</v>
+        <v>11695516.22</v>
       </c>
       <c r="S3" t="n">
-        <v>-3775000</v>
+        <v>115309709.42</v>
       </c>
       <c r="T3" t="n">
-        <v>1225000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-5000000</v>
-      </c>
+        <v>115309709.42</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-818548529.1799999</v>
+        <v>-382230875.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>64434</v>
+        <v>443394.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>-818612963.1799999</v>
+        <v>-382674269.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>166771139.68</v>
+        <v>108812390.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>-40193530.39</v>
+        <v>-43500900.82</v>
       </c>
       <c r="AC3" t="n">
-        <v>-7935773.71</v>
+        <v>-8174233.39</v>
       </c>
       <c r="AD3" t="n">
-        <v>87006387.48999999</v>
+        <v>13071347.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>-14575294.49</v>
+        <v>3256966.45</v>
       </c>
       <c r="AF3" t="n">
-        <v>-104688849.68</v>
+        <v>-51654981.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>6146870.02</v>
+        <v>1624137.09</v>
       </c>
       <c r="AH3" t="n">
-        <v>55735054.16</v>
+        <v>50316355.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>5769116.82</v>
+        <v>3637164.97</v>
       </c>
       <c r="AJ3" t="n">
-        <v>49965937.34</v>
+        <v>46679190.41</v>
       </c>
       <c r="AK3" t="n">
-        <v>-403806.38</v>
+        <v>-1916867.92</v>
       </c>
       <c r="AL3" t="n">
-        <v>929428.61</v>
+        <v>1200081.45</v>
       </c>
       <c r="AM3" t="n">
-        <v>90524380.83</v>
+        <v>91261076.04000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>166771139.68</v>
+        <v>108812390.03</v>
       </c>
       <c r="AO3" t="n">
-        <v>-338701417.71</v>
+        <v>-117087617.44</v>
       </c>
       <c r="AP3" t="n">
-        <v>-3137243896.57</v>
+        <v>-3298164280.36</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-371723481.87</v>
+        <v>-120510217.77</v>
       </c>
       <c r="AR3" t="n">
-        <v>-138001632</v>
+        <v>-128704038.48</v>
       </c>
       <c r="AS3" t="n">
-        <v>-2627518782.7</v>
+        <v>-3048950024.11</v>
       </c>
       <c r="AT3" t="n">
-        <v>3642716453.96</v>
+        <v>3524064287.83</v>
       </c>
       <c r="AU3" t="n">
-        <v>354162109.07</v>
+        <v>64067483.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>3288554344.89</v>
+        <v>3459996803.95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-273861879.64</v>
+        <v>-651841823.5</v>
       </c>
       <c r="C4" t="n">
-        <v>-10500000</v>
+        <v>-80500000</v>
       </c>
       <c r="D4" t="n">
-        <v>57000000</v>
+        <v>610264822.12</v>
       </c>
       <c r="E4" t="n">
-        <v>-382674269.67</v>
+        <v>-818612963.1799999</v>
       </c>
       <c r="F4" t="n">
+        <v>1101503463.97</v>
+      </c>
+      <c r="G4" t="n">
         <v>216120894.58</v>
       </c>
-      <c r="G4" t="n">
-        <v>242141097.42</v>
-      </c>
       <c r="H4" t="n">
-        <v>1016668.09</v>
+        <v>-142179.04</v>
       </c>
       <c r="I4" t="n">
-        <v>-27036870.93</v>
+        <v>885524748.4299999</v>
       </c>
       <c r="J4" t="n">
-        <v>119376388.57</v>
+        <v>1540474701.68</v>
       </c>
       <c r="K4" t="n">
-        <v>73300931.59999999</v>
+        <v>1016104011.11</v>
       </c>
       <c r="L4" t="n">
-        <v>-424543.03</v>
+        <v>-5394131.55</v>
       </c>
       <c r="M4" t="n">
-        <v>46500000</v>
+        <v>529764822.12</v>
       </c>
       <c r="N4" t="n">
-        <v>46500000</v>
+        <v>529764822.12</v>
       </c>
       <c r="O4" t="n">
-        <v>-10500000</v>
+        <v>-80500000</v>
       </c>
       <c r="P4" t="n">
-        <v>57000000</v>
+        <v>610264822.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>-255225649.53</v>
+        <v>-821721092.9299999</v>
       </c>
       <c r="R4" t="n">
-        <v>11695516.22</v>
+        <v>602436.25</v>
       </c>
       <c r="S4" t="n">
-        <v>115309709.42</v>
+        <v>-3775000</v>
       </c>
       <c r="T4" t="n">
-        <v>115309709.42</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>1225000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-5000000</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-382230875.17</v>
+        <v>-818548529.1799999</v>
       </c>
       <c r="Y4" t="n">
-        <v>443394.5</v>
+        <v>64434</v>
       </c>
       <c r="Z4" t="n">
-        <v>-382674269.67</v>
+        <v>-818612963.1799999</v>
       </c>
       <c r="AA4" t="n">
-        <v>108812390.03</v>
+        <v>166771139.68</v>
       </c>
       <c r="AB4" t="n">
-        <v>-43500900.82</v>
+        <v>-40193530.39</v>
       </c>
       <c r="AC4" t="n">
-        <v>-8174233.39</v>
+        <v>-7935773.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>13071347.9</v>
+        <v>87006387.48999999</v>
       </c>
       <c r="AE4" t="n">
-        <v>3256966.45</v>
+        <v>-14575294.49</v>
       </c>
       <c r="AF4" t="n">
-        <v>-51654981.78</v>
+        <v>-104688849.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>1624137.09</v>
+        <v>6146870.02</v>
       </c>
       <c r="AH4" t="n">
-        <v>50316355.38</v>
+        <v>55735054.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>3637164.97</v>
+        <v>5769116.82</v>
       </c>
       <c r="AJ4" t="n">
-        <v>46679190.41</v>
+        <v>49965937.34</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1916867.92</v>
+        <v>-403806.38</v>
       </c>
       <c r="AL4" t="n">
-        <v>1200081.45</v>
+        <v>929428.61</v>
       </c>
       <c r="AM4" t="n">
-        <v>91261076.04000001</v>
+        <v>90524380.83</v>
       </c>
       <c r="AN4" t="n">
-        <v>108812390.03</v>
+        <v>166771139.68</v>
       </c>
       <c r="AO4" t="n">
-        <v>-117087617.44</v>
+        <v>-338701417.71</v>
       </c>
       <c r="AP4" t="n">
-        <v>-3298164280.36</v>
+        <v>-3137243896.57</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-120510217.77</v>
+        <v>-371723481.87</v>
       </c>
       <c r="AR4" t="n">
-        <v>-128704038.48</v>
+        <v>-138001632</v>
       </c>
       <c r="AS4" t="n">
-        <v>-3048950024.11</v>
+        <v>-2627518782.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>3524064287.83</v>
+        <v>3642716453.96</v>
       </c>
       <c r="AU4" t="n">
-        <v>64067483.88</v>
+        <v>354162109.07</v>
       </c>
       <c r="AV4" t="n">
-        <v>3459996803.95</v>
+        <v>3288554344.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-303205510.11</v>
+        <v>-425429785.06</v>
       </c>
       <c r="C5" t="n">
-        <v>-5000000</v>
+        <v>-536974520.15</v>
       </c>
       <c r="D5" t="n">
-        <v>10000000</v>
+        <v>189769970.75</v>
       </c>
       <c r="E5" t="n">
-        <v>-357111195.6</v>
+        <v>-459897026.58</v>
       </c>
       <c r="F5" t="n">
-        <v>242141097.42</v>
+        <v>274382882.54</v>
       </c>
       <c r="G5" t="n">
-        <v>272425613.46</v>
+        <v>1101503463.97</v>
       </c>
       <c r="H5" t="n">
-        <v>34427.88</v>
+        <v>32577.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-30318943.92</v>
+        <v>-827153159.13</v>
       </c>
       <c r="J5" t="n">
-        <v>-1738743.64</v>
+        <v>-359285823.77</v>
       </c>
       <c r="K5" t="n">
-        <v>-3373234.14</v>
+        <v>33479602.6</v>
       </c>
       <c r="L5" t="n">
-        <v>-3365509.5</v>
+        <v>-45560876.97</v>
       </c>
       <c r="M5" t="n">
-        <v>5000000</v>
+        <v>-347204549.4</v>
       </c>
       <c r="N5" t="n">
-        <v>5000000</v>
+        <v>-347204549.4</v>
       </c>
       <c r="O5" t="n">
-        <v>-5000000</v>
+        <v>-536974520.15</v>
       </c>
       <c r="P5" t="n">
-        <v>10000000</v>
+        <v>189769970.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>-82485885.77</v>
-      </c>
-      <c r="R5" t="n">
-        <v>304753166.48</v>
-      </c>
+        <v>-502334576.88</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-31074193.65</v>
+        <v>-57775000</v>
       </c>
       <c r="T5" t="n">
-        <v>203659743.35</v>
+        <v>1225000</v>
       </c>
       <c r="U5" t="n">
-        <v>-234733937</v>
-      </c>
-      <c r="V5" t="n">
-        <v>313565.34</v>
-      </c>
-      <c r="W5" t="n">
-        <v>313565.34</v>
-      </c>
+        <v>-59000000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-356478423.94</v>
+        <v>-444559576.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>632771.66</v>
+        <v>15337449.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>-357111195.6</v>
+        <v>-459897026.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>53905685.49</v>
+        <v>34467241.52</v>
       </c>
       <c r="AB5" t="n">
-        <v>-42264367.54</v>
+        <v>-139481751.94</v>
       </c>
       <c r="AC5" t="n">
-        <v>1680062.96</v>
+        <v>-4444175.69</v>
       </c>
       <c r="AD5" t="n">
-        <v>38767069.54</v>
+        <v>30385536.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>-24235407.55</v>
+        <v>-135406384.79</v>
       </c>
       <c r="AF5" t="n">
-        <v>-58476092.49</v>
+        <v>-30016727.96</v>
       </c>
       <c r="AG5" t="n">
-        <v>4939765.5</v>
+        <v>6678438.54</v>
       </c>
       <c r="AH5" t="n">
-        <v>27204844.36</v>
+        <v>94307941.86</v>
       </c>
       <c r="AI5" t="n">
-        <v>2752801.41</v>
+        <v>6977650.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24452042.95</v>
+        <v>87330290.95999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>-5978680.75</v>
+        <v>-705882.63</v>
       </c>
       <c r="AL5" t="n">
-        <v>1699472.5</v>
+        <v>-4207286.14</v>
       </c>
       <c r="AM5" t="n">
-        <v>72615084.44</v>
+        <v>53231432.07</v>
       </c>
       <c r="AN5" t="n">
-        <v>53905685.49</v>
+        <v>34467241.52</v>
       </c>
       <c r="AO5" t="n">
-        <v>-31595499.2</v>
+        <v>-545622122.97</v>
       </c>
       <c r="AP5" t="n">
-        <v>-2072263424.89</v>
+        <v>-3690697504.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-87206563.54000001</v>
+        <v>-147985815.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>-107555788.14</v>
+        <v>-158850561.12</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1877501073.21</v>
+        <v>-3383861127.73</v>
       </c>
       <c r="AT5" t="n">
-        <v>2157764609.58</v>
+        <v>4270786868.69</v>
       </c>
       <c r="AU5" t="n">
-        <v>22955655.71</v>
+        <v>107523271.59</v>
       </c>
       <c r="AV5" t="n">
-        <v>2134808953.87</v>
+        <v>4163263597.1</v>
       </c>
     </row>
   </sheetData>
@@ -4016,182 +4016,182 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Feng  Fu', 'age': 51, 'title': 'GM &amp; Director', 'yearBorn': 1974, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xiang Bo  Li', 'age': 49, 'title': 'Financial Director &amp; Deputy General Manager', 'yearBorn': 1976, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Haibo  Zou', 'age': 52, 'title': 'Deputy GM, Board Secretary &amp; Director', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guo Liang  Huo', 'age': 51, 'title': 'Deputy General Manager', 'yearBorn': 1974, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Min  Tan', 'title': 'Accounting Supervisor', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -4286,34 +4286,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>15.37</v>
+        <v>13.26</v>
       </c>
       <c r="T2" t="n">
-        <v>15.53</v>
+        <v>13.3</v>
       </c>
       <c r="U2" t="n">
-        <v>14.66</v>
+        <v>12.65</v>
       </c>
       <c r="V2" t="n">
-        <v>15.53</v>
+        <v>13.28</v>
       </c>
       <c r="W2" t="n">
-        <v>15.37</v>
+        <v>13.26</v>
       </c>
       <c r="X2" t="n">
-        <v>15.53</v>
+        <v>13.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.66</v>
+        <v>12.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.53</v>
+        <v>13.28</v>
       </c>
       <c r="AA2" t="n">
         <v>0.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="AC2" t="n">
         <v>1752192000</v>
@@ -4325,37 +4325,37 @@
         <v>0.37</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.588</v>
+        <v>0.497</v>
       </c>
       <c r="AG2" t="n">
-        <v>7773384</v>
+        <v>6543861</v>
       </c>
       <c r="AH2" t="n">
-        <v>7773384</v>
+        <v>6543861</v>
       </c>
       <c r="AI2" t="n">
-        <v>10309057</v>
+        <v>8023187</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12032158</v>
+        <v>5945782</v>
       </c>
       <c r="AK2" t="n">
-        <v>12032158</v>
+        <v>5945782</v>
       </c>
       <c r="AL2" t="n">
-        <v>14.82</v>
+        <v>13.05</v>
       </c>
       <c r="AM2" t="n">
-        <v>14.83</v>
+        <v>13.06</v>
       </c>
       <c r="AN2" t="n">
-        <v>5479751680</v>
+        <v>4822033920</v>
       </c>
       <c r="AO2" t="n">
-        <v>5479751823</v>
+        <v>4899629749</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.9</v>
+        <v>12.65</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
@@ -4367,13 +4367,13 @@
         <v>2.246971</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.4675465</v>
+        <v>1.2914014</v>
       </c>
       <c r="AU2" t="n">
-        <v>15.6032</v>
+        <v>15.4212</v>
       </c>
       <c r="AV2" t="n">
-        <v>16.6962</v>
+        <v>16.48085</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>6090805248</v>
+        <v>5433087488</v>
       </c>
       <c r="BB2" t="n">
         <v>-0.01684</v>
@@ -4402,7 +4402,7 @@
         <v>369504506</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.44089</v>
+        <v>0.41612</v>
       </c>
       <c r="BF2" t="n">
         <v>0.019270001</v>
@@ -4414,7 +4414,7 @@
         <v>5.626</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.6359758</v>
+        <v>2.3195877</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
@@ -4443,16 +4443,16 @@
         <v>1591920000</v>
       </c>
       <c r="BR2" t="n">
-        <v>1.631</v>
+        <v>1.455</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.017</v>
+        <v>69.592</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.046577334</v>
+        <v>-0.12877792</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.1</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="BY2" t="n">
-        <v>14.83</v>
+        <v>13.05</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -4570,135 +4570,135 @@
       </c>
       <c r="DB2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>1782111882</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>finmb_5723123</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DF2" t="n">
+      <c r="DH2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DH2" t="b">
+      <c r="DJ2" t="b">
         <v>0</v>
       </c>
-      <c r="DI2" t="n">
-        <v>-3.5133374</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>14.83</v>
-      </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1780038297</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DN2" t="b">
+          <t>Yueyang Xingchang Petro-Chemical Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>YUEYANG XINGCHANG PETRO CHEMICA</t>
+        </is>
+      </c>
+      <c r="DM2" t="b">
         <v>0</v>
       </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
+      <c r="DN2" t="n">
         <v>867202200000</v>
       </c>
-      <c r="DQ2" t="n">
-        <v>-0.5399999599999999</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>14.66 - 15.53</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DO2" t="n">
+        <v>-0.21000004</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>12.65 - 13.28</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
+      <c r="DR2" t="n">
+        <v>8023187</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.40000057</v>
+      </c>
       <c r="DT2" t="n">
-        <v>10309057</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.9300003</v>
+        <v>0.0316206</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>12.65 - 21.0</t>
+        </is>
       </c>
       <c r="DV2" t="n">
-        <v>0.06690649999999999</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>13.9 - 21.0</t>
-        </is>
+        <v>-7.95</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.37857142</v>
       </c>
       <c r="DX2" t="n">
-        <v>-6.17</v>
+        <v>-12.877792</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0.29380953</v>
+        <v>1619607540</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.6577334</v>
+        <v>1619607540</v>
       </c>
       <c r="EA2" t="n">
-        <v>1619607540</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1619607540</v>
+        <v>-0.17</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
       </c>
       <c r="EC2" t="n">
-        <v>-0.17</v>
+        <v>-2.3711996</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0.77320004</v>
+        <v>-0.15376233</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.04955394</v>
+        <v>-3.43085</v>
       </c>
       <c r="EF2" t="n">
-        <v>-1.8661995</v>
+        <v>-0.2081719</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.11177391</v>
+        <v>15</v>
       </c>
       <c r="EH2" t="n">
         <v>15</v>
       </c>
-      <c r="EI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>YUEYANG XINGCHANG PETRO CHEMICA</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>Yueyang Xingchang Petro-Chemical Co., Ltd.</t>
-        </is>
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-1.5837107</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>13.05</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
